--- a/Project/01. Payment Block/Desktop Files/RAP Conversion/01. Tables.xlsx
+++ b/Project/01. Payment Block/Desktop Files/RAP Conversion/01. Tables.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Others\RAP Conversion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05. Daily (21-Mar-26) - 6GB\VSCode\Project\01. Payment Block\Desktop Files\RAP Conversion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF69EE83-CD1C-4B90-896D-24377206F707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6BECCF-F06E-42EF-87CD-750B0EC68372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{9C93B85F-C357-42EB-A221-D69E92FACD24}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{9C93B85F-C357-42EB-A221-D69E92FACD24}"/>
   </bookViews>
   <sheets>
     <sheet name="Z2A_T_PAY_BLOCK" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
     <sheet name="ZCY_TAB_RRP_E" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
+    <sheet name="RRP_E New" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="1156">
   <si>
     <t>{</t>
   </si>
@@ -3756,6 +3757,762 @@
   </si>
   <si>
     <t>c8</t>
+  </si>
+  <si>
+    <t>@EndUserText.label : 'Regular Returns Purchase Export.'</t>
+  </si>
+  <si>
+    <t>@AbapCatalog.tableCategory : #TRANSPARENT</t>
+  </si>
+  <si>
+    <t>@AbapCatalog.deliveryClass : #A</t>
+  </si>
+  <si>
+    <t>@AbapCatalog.dataMaintenance : #ALLOWED</t>
+  </si>
+  <si>
+    <t>define table zcy_tab_rrp_e {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  key mandt                      : mandt not null;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  key custom1                    : zcy_det_custom1 not null;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  key custom4                    : zcy_det_custom4 not null;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  key custom9                    : zcy_det_custom9 not null;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  returnperiod                   : zcy_det_returnperiod;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  locationgstin                  : zcy_det_locationgstin;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  documentnumber                 : zcy_det_documentnumber;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  serialnumber                   : zcy_det_serialnumber;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  documentdate                   : bldat;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromgstin                  : zcy_det_billfromgstin;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  financialyear                  : zcy_det_financialyear;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  mapperid                       : zcy_det_mapperid;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  supplytype                     : zcy_det_supplytype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  purpose                        : zcy_det_purpose;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  locationname                   : zcy_det_locationname;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  irn                            : zcy_det_irn;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  liabilitydischargereturnperiod : zcy_det_liabilitydischargeretu;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  itcclaimreturnperiod           : zcy_det_itcclaimreturnperiod;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  documenttype                   : zcy_det_documenttype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  transactiontype                : zcy_det_transactiontype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  taxpayertype                   : zcy_det_taxpayertype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  transactionnature              : zcy_det_transactionnature;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  documentseriescode             : zcy_det_documentseriescode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromlegalname              : zcy_det_billfromlegalname;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromtradename              : zcy_det_billfromtradename;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromvendorcode             : zcy_det_billfromvendorcode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromaddress1               : zcy_det_billfromaddress1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromaddress2               : zcy_det_billfromaddress2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromcity                   : zcy_det_billfromcity;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromstatecode              : zcy_det_billfromstatecode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfrompincode                : zcy_det_billfrompincode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromphone                  : zcy_det_billfromphone;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billfromemail                  : zcy_det_billfromemail;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  dispatchfromgstin              : zcy_det_dispatchfromgstin;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  dispatchfromtradename          : zcy_det_dispatchfromtradename;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  dispatchfromvendorcode         : zcy_det_dispatchfromvendorcode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  dispatchfromaddress1           : zcy_det_dispatchfromaddress1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  dispatchfromaddress2           : zcy_det_dispatchfromaddress2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  dispatchfromcity               : zcy_det_dispatchfromcity;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  dispatchfromstatecode          : zcy_det_dispatchfromstatecode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  dispatchfrompincode            : zcy_det_dispatchfrompincode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtogstin                    : zcy_det_billtogstin;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtolegalname                : zcy_det_billtolegalname;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtotradename                : zcy_det_billtotradename;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtovendorcode               : zcy_det_billtovendorcode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtoaddress1                 : zcy_det_billtoaddress1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtoaddress2                 : zcy_det_billtoaddress2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtocity                     : zcy_det_billtocity;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtostatecode                : zcy_det_billtostatecode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtopincode                  : zcy_det_billtopincode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtophone                    : zcy_det_billtophone;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  billtoemail                    : zcy_det_billtoemail;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shiptogstin                    : zcy_det_shiptogstin;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shiptolegalname                : zcy_det_shiptolegalname;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shiptotradename                : zcy_det_shiptotradename;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shiptovendorcode               : zcy_det_shiptovendorcode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shiptoaddress1                 : zcy_det_shiptoaddress1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shiptoaddress2                 : zcy_det_shiptoaddress2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shiptocity                     : zcy_det_shiptocity;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shiptostatecode                : zcy_det_shiptostatecode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shiptopincode                  : zcy_det_shiptopincode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  paymenttype                    : zcy_det_paymenttype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  paymentmode                    : zcy_det_paymentmode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  @Semantics.amount.currencyCode : 'vbak.waerk'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  paymentamount                  : zcy_det_paymentamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  advancepaidamount              : zcy_det_advancepaidamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  paymentdate                    : zcy_det_paymentdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  paymentremarks                 : zcy_det_paymentremarks;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  paymentterms                   : zcy_det_paymentterms;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  paymentinstruction             : zcy_det_paymentinstruction;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  payeename                      : zcy_det_payeename;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  payeeaccountnumber             : zcy_det_payeeaccountnumber;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  paymentamountdue               : zcy_det_paymentamountdue;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ifsc                           : zcy_det_ifsc;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  credittransfer                 : zcy_det_credittransfer;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  directdebit                    : zcy_det_directdebit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  creditdays                     : zcy_det_creditdays;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  creditavaileddate              : zcy_det_creditavaileddate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  creditreversaldate             : zcy_det_creditreversaldate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  refdocumentremarks             : zcy_det_refdocumentremarks;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  refdocumentperiodstartdate     : zcy_det_refdocumentperiodstart;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  refdocumentperiodenddate       : zcy_det_refdocumentperiodendda;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  invno                          : zcy_det_invno;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  invdt                          : zcy_det_invdt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  refcontractdetails             : zcy_det_refcontractdetails;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  additionalsupportingdocumentde : zcy_det_additionalsupportingdo;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  portcode                       : zcy_det_portcode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  documentcurrencycode           : zcy_det_documentcurrencycode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  destinationcountry             : zcy_det_destinationcountry;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  pos                            : zcy_det_pos;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  documentvalue                  : zcy_det_documentvalue;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  documentdiscount               : zcy_det_documentdiscount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  documentothercharges           : zcy_det_documentothercharges;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  documentvalueinforeigncurrency : zcy_det_documentvalueinforeign;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  roundoffamount                 : zcy_det_roundoffamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  differentialpercentage         : zcy_det_differentialpercentage;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  reversecharge                  : zcy_det_reversecharge;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  claimrefund                    : zcy_det_claimrefund;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  underigstact                   : zcy_det_underigstact;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  refundeligibility              : zcy_det_refundeligibility;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  pnroruniquenumber              : zcy_det_pnroruniquenumber;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  availprovisionalitc            : zcy_det_availprovisionalitc;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  originalstatecode              : zcy_det_originalstatecode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  originaldocumentnumber         : zcy_det_originaldocumentnumber;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  originaldocumentdate           : zcy_det_originaldocumentdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  originalreturnperiod           : zcy_det_originalreturnperiod;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  originaltaxablevalue           : zcy_det_originaltaxablevalue;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  toemailaddresses               : zcy_det_toemailaddresses;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  tomobilenumbers                : zcy_det_tomobilenumbers;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  jworiginaldocumentnumber       : zcy_det_jworiginaldocumentnumb;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  jworiginaldocumentdate         : zcy_det_jworiginaldocumentdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  jwdocumentnumber               : zcy_det_jwdocumentnumber;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  jwdocumentdate                 : zcy_det_jwdocumentdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  autodraftsource                : zcy_det_autodraftsource;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  irngenerationdate              : zcy_det_irngenerationdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  isamendment                    : zcy_det_isamendment;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  isavailableingstr2b            : zcy_det_isavailableingstr2b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  itcavailability                : zcy_det_itcavailability;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  itcunavailabilityreason        : zcy_det_itcunavailabilityreaso;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  custom2                        : zcy_det_custom2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  custom3                        : zcy_det_custom3;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  custom5                        : zcy_det_custom5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  custom6                        : zcy_det_custom6;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  custom7                        : zcy_det_custom7;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  custom8                        : zcy_det_custom8;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  custom10                       : zcy_det_custom10;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  custom20                       : zcy_det_custom20;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  natureofjwdone                 : zcy_det_natureofjwdone;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  lossunitofmeasure              : zcy_det_lossunitofmeasure;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  @Semantics.quantity.unitOfMeasure : 'vbap.zieme'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  losstotalquantity              : zcy_det_losstotalquantity;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  pusherrors                     : zcy_det_pusherrors;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  pushstatus                     : zcy_det_pushstatus;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gstaction                      : zcy_det_gstaction;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  reconciliationsection          : zcy_det_reconciliationsection;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  pushdate                       : zcy_det_pushdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cancelleddate                  : zcy_det_cancelleddate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ispregstregime                 : zcy_det_ispregstregime;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  amendedtype                    : zcy_det_amendedtype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  isgstr3bfiled                  : zcy_det_isgstr3bfiled;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  isgstr3bfildate                : zcy_det_is3bfilingdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  filingdate                     : zcy_det_filingdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  filingreturnperiod             : zcy_det_filingreturnperiod;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  filingstatus                   : zcy_det_filingstatus;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  isservice                      : zcy_det_isservice;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  hsn                            : zcy_det_hsn;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  productcode                    : zcy_det_productcode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  name                           : zcy_det_name;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  description                    : zcy_det_description;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  barcode                        : zcy_det_barcode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  uqc                            : zcy_det_uqc;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  quantity                       : zcy_det_quantity;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  freequantity                   : zcy_det_freequantity;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  @Semantics.amount.currencyCode : 'rv61a.koei1'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  rate                           : zcy_det_rate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cessrate                       : zcy_det_cessrate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  statecessrate                  : zcy_det_statecessrate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cessnonadvaloremrate           : zcy_det_cessnonadvaloremrate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  priceperquantity               : zcy_det_priceperquantity;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  @Semantics.amount.currencyCode : 'komk.waerk'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  discountamount                 : zcy_det_discountamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  grossamount                    : zcy_det_grossamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  othercharges                   : zcy_det_othercharges;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  taxablevalue                   : zcy_det_taxablevalue;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  igstamount                     : zcy_det_igstamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cgstamount                     : zcy_det_cgstamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  sgstamount                     : zcy_det_sgstamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cessamount                     : zcy_det_cessamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  statecessamount                : zcy_det_statecessamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cessnonadvaloremamount         : zcy_det_cessnonadvaloremamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  statecessnonadvaloremamount    : zcy_det_statecessnonadvalorema;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  taxtype                        : zcy_det_taxtype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  itceligibility                 : zcy_det_itceligibility;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  itcigstamount                  : zcy_det_itcigstamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  itccgstamount                  : zcy_det_itccgstamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  itcsgstamount                  : zcy_det_itcsgstamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  itccessamount                  : zcy_det_itccessamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem1                    : zcy_det_customitem1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem2                    : zcy_det_customitem2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem3                    : zcy_det_customitem3;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem4                    : zcy_det_customitem4;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem5                    : zcy_det_customitem5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem6                    : zcy_det_customitem6;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem7                    : zcy_det_customitem7;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem8                    : zcy_det_customitem8;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem9                    : zcy_det_customitem9;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  customitem10                   : zcy_det_customitem10;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpgstin                        : zcy_det_cpgstin;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cptradename                    : zcy_det_cptradename;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cplegalname                    : zcy_det_cplegalname;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cporiginaldocumentnumber       : zcy_det_cporiginaldocumentnum;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cporiginaldocumentdate         : zcy_det_cporiginaldocumentdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpportcode                     : zcy_det_cpportcode;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpdocumentnumber               : zcy_det_cpdocumentnumber;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpdocumentdate                 : zcy_det_cpdocumentdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpvalue                        : zcy_det_cpvalue;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cppos                          : zcy_det_cppos;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpreversecharge                : zcy_det_cpreversecharge;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpdifferentialpercentage       : zcy_det_cpdifferentialpercent;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cptransactiontype              : zcy_det_cptransactiontype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cptaxpayertype                 : zcy_det_cptaxpayertype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cptaxablevalue                 : zcy_det_cptaxablevalue;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cprate                         : zcy_det_cprate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpigstamount                   : zcy_det_cpigstamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpcgstamount                   : zcy_det_cpcgstamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpsgstamount                   : zcy_det_cpsgstamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpcessamount                   : zcy_det_cpcessamount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpfilingstatus                 : zcy_det_cpfilingstatus;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpsuppliercancellationdate     : zcy_det_cpsuppliercancellation;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpfilingdate                   : zcy_det_cpfilingdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpfilingreturnperiod           : zcy_det_cpfilingreturnperiod;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpautodraftsource              : zcy_det_cpautodraftsource;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpirn                          : zcy_det_cpirn;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpirngenerationdate            : zcy_det_cpirngenerationdate;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cprefprecedingdocumentdetails  : zcy_det_cprefprecedingdocument;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpavailableingstr2b            : zcy_det_cpavailableingstr2b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpgstr2breturnperiod           : zcy_det_cpgstr2breturnperiod;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpavailableingstr98a           : zcy_det_cpavailableingstr98a;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpitcavailability              : zcy_det_cpitcavailability;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpitcunavailabilityreason      : zcy_det_cpitcunavailabilityrea;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpitcclaimmonth                : zcy_det_cpitcclaimmonth;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpreturnperiod                 : zcy_det_cpreturnperiod;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpisamendment                  : zcy_det_cpisamendment;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cporiginalreturnperiod         : zcy_det_cporiginalreturnperiod;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cpamendedtype                  : zcy_det_cpamendedtype;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  valuediff                      : zcy_det_valuediff;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  taxablediff                    : zcy_det_taxablediff;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  taxdiff                        : zcy_det_taxdiff;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  reason                         : zcy_det_reason;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  rec_date                       : datum;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  rec_time                       : uzeit;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  p_pbf                          : abap_boolean;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  p_jv                           : abap_boolean;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  p_dbf                          : abap_boolean;</t>
+  </si>
+  <si>
+    <t>c13</t>
+  </si>
+  <si>
+    <t>c70</t>
+  </si>
+  <si>
+    <t>c10</t>
+  </si>
+  <si>
+    <t>c12</t>
+  </si>
+  <si>
+    <t>c18</t>
+  </si>
+  <si>
+    <t>cur 13,2</t>
+  </si>
+  <si>
+    <t>c11</t>
+  </si>
+  <si>
+    <t>c5</t>
+  </si>
+  <si>
+    <t>quan 13,3</t>
+  </si>
+  <si>
+    <t>c30</t>
+  </si>
+  <si>
+    <t>c14</t>
+  </si>
+  <si>
+    <t>c7</t>
+  </si>
+  <si>
+    <t>c64</t>
   </si>
 </sst>
 </file>
@@ -12971,6 +13728,2001 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C50D53-0415-4A98-8ADF-E39E88A94125}">
+  <dimension ref="B2:I268"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>910</v>
+      </c>
+      <c r="I10" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>911</v>
+      </c>
+      <c r="I11" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>912</v>
+      </c>
+      <c r="I12" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>913</v>
+      </c>
+      <c r="I13" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>914</v>
+      </c>
+      <c r="I14" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>915</v>
+      </c>
+      <c r="I15" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>916</v>
+      </c>
+      <c r="I16" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>918</v>
+      </c>
+      <c r="I18" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>919</v>
+      </c>
+      <c r="I19" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>920</v>
+      </c>
+      <c r="I20" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>921</v>
+      </c>
+      <c r="I21" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>922</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>923</v>
+      </c>
+      <c r="I23" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>924</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>925</v>
+      </c>
+      <c r="I25" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>926</v>
+      </c>
+      <c r="I26" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>927</v>
+      </c>
+      <c r="I27" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>928</v>
+      </c>
+      <c r="I28" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>929</v>
+      </c>
+      <c r="I29" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>930</v>
+      </c>
+      <c r="I30" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>931</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>932</v>
+      </c>
+      <c r="I32" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>933</v>
+      </c>
+      <c r="I33" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>934</v>
+      </c>
+      <c r="I34" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>935</v>
+      </c>
+      <c r="I35" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>936</v>
+      </c>
+      <c r="I36" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>937</v>
+      </c>
+      <c r="I37" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>938</v>
+      </c>
+      <c r="I38" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>939</v>
+      </c>
+      <c r="I39" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>940</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>941</v>
+      </c>
+      <c r="I41" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>942</v>
+      </c>
+      <c r="I42" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>943</v>
+      </c>
+      <c r="I43" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>944</v>
+      </c>
+      <c r="I44" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>945</v>
+      </c>
+      <c r="I45" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>946</v>
+      </c>
+      <c r="I46" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>948</v>
+      </c>
+      <c r="I48" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>949</v>
+      </c>
+      <c r="I49" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>950</v>
+      </c>
+      <c r="I50" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>951</v>
+      </c>
+      <c r="I51" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>952</v>
+      </c>
+      <c r="I52" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>953</v>
+      </c>
+      <c r="I53" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>954</v>
+      </c>
+      <c r="I54" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>955</v>
+      </c>
+      <c r="I55" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>956</v>
+      </c>
+      <c r="I56" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>959</v>
+      </c>
+      <c r="I59" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>960</v>
+      </c>
+      <c r="I60" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>961</v>
+      </c>
+      <c r="I61" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>962</v>
+      </c>
+      <c r="I62" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>963</v>
+      </c>
+      <c r="I63" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>964</v>
+      </c>
+      <c r="I64" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>965</v>
+      </c>
+      <c r="I65" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>966</v>
+      </c>
+      <c r="I66" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>967</v>
+      </c>
+      <c r="I67" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>968</v>
+      </c>
+      <c r="I68" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>969</v>
+      </c>
+      <c r="I69" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>970</v>
+      </c>
+      <c r="I70" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>971</v>
+      </c>
+      <c r="I71" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>973</v>
+      </c>
+      <c r="I73" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>974</v>
+      </c>
+      <c r="I75" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>975</v>
+      </c>
+      <c r="I76" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>976</v>
+      </c>
+      <c r="I77" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>977</v>
+      </c>
+      <c r="I78" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>978</v>
+      </c>
+      <c r="I79" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>979</v>
+      </c>
+      <c r="I80" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>980</v>
+      </c>
+      <c r="I81" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>981</v>
+      </c>
+      <c r="I83" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>982</v>
+      </c>
+      <c r="I84" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>983</v>
+      </c>
+      <c r="I85" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>984</v>
+      </c>
+      <c r="I86" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>985</v>
+      </c>
+      <c r="I87" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>986</v>
+      </c>
+      <c r="I88" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>987</v>
+      </c>
+      <c r="I89" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>988</v>
+      </c>
+      <c r="I90" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>989</v>
+      </c>
+      <c r="I91" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>990</v>
+      </c>
+      <c r="I92" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>991</v>
+      </c>
+      <c r="I93" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>992</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>993</v>
+      </c>
+      <c r="I95" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>994</v>
+      </c>
+      <c r="I96" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>995</v>
+      </c>
+      <c r="I97" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>996</v>
+      </c>
+      <c r="I98" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>997</v>
+      </c>
+      <c r="I99" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>998</v>
+      </c>
+      <c r="I100" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>999</v>
+      </c>
+      <c r="I102" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I103" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I104" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I106" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I108" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I109" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I110" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I111" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I112" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I113" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I114" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I115" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I116" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I117" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I118" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I119" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I121" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I122" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I123" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I124" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I125" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I126" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I127" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I128" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I129" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I130" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I131" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I132" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I133" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I134" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I135" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I136" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I137" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I138" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I139" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I140" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I141" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I142" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I143" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I145" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I146" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I147" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I148" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I149" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I150" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I151" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I152" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I153" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I154" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I155" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I156" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I157" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I158" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I159" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I160" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I161" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I162" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I163" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>1058</v>
+      </c>
+      <c r="I164" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I165" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I167" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I168" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I170" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B172" t="s">
+        <v>1064</v>
+      </c>
+      <c r="I172" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
+        <v>1065</v>
+      </c>
+      <c r="I173" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B174" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B175" t="s">
+        <v>1066</v>
+      </c>
+      <c r="I175" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I176" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B177" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I178" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B179" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I180" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B181" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I181" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B182" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B183" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I183" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B184" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B185" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I185" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B186" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B187" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I187" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B188" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B189" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I189" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B190" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B191" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I191" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B192" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B193" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I193" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B194" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B195" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I195" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B196" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I196" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B197" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I197" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B198" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I198" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B199" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B200" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I200" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B201" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B202" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I202" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B203" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B204" t="s">
+        <v>1084</v>
+      </c>
+      <c r="I204" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B205" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="206" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B206" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I206" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B207" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I207" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B208" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I208" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="209" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B209" t="s">
+        <v>1088</v>
+      </c>
+      <c r="I209" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="210" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B210" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I210" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="211" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B211" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I211" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="212" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B212" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I212" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="213" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B213" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I213" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="214" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B214" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I214" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="215" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B215" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I215" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="216" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B216" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I216" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="217" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B217" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I217" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="218" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B218" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I218" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="219" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B219" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I219" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="220" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B220" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I220" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="221" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B221" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I221" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="222" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B222" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I222" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="223" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B223" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I223" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="224" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B224" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I224" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="225" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B225" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I225" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="226" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B226" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I226" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="227" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B227" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I227" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="228" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B228" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I228" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="229" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B229" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I229" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="230" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B230" t="s">
+        <v>1109</v>
+      </c>
+      <c r="I230" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="231" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B231" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I231" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="232" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B232" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I232" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="233" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B233" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I233" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="234" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B234" t="s">
+        <v>1113</v>
+      </c>
+      <c r="I234" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="235" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B235" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I235" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="236" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B236" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I236" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="237" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B237" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I237" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="238" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B238" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I238" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="239" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B239" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I239" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="240" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B240" t="s">
+        <v>1119</v>
+      </c>
+      <c r="I240" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="241" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B241" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I241" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="242" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B242" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I242" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="243" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B243" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I243" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="244" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B244" t="s">
+        <v>1123</v>
+      </c>
+      <c r="I244" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="245" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B245" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I245" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="246" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B246" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I246" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="247" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B247" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I247" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="248" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B248" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I248" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="249" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B249" t="s">
+        <v>1128</v>
+      </c>
+      <c r="I249" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="250" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B250" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I250" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="251" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B251" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I251" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="252" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B252" t="s">
+        <v>1131</v>
+      </c>
+      <c r="I252" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="253" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B253" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I253" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="254" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B254" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I254" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="255" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B255" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="256" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B256" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I256" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="257" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B257" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="258" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B258" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I258" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="259" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B259" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="260" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B260" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I260" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="261" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B261" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I261" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="262" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B262" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="263" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B263" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="264" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B264" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="265" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B265" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="266" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B266" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="268" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B268" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{084C4509-7839-4AD6-BF70-D3BB859D1A73}">
   <dimension ref="E3:Q229"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
